--- a/Teoría de la información/AF2/Canal Binario Simétrico/Ejercicio D - Caracter difuso convertido a 1.xlsx
+++ b/Teoría de la información/AF2/Canal Binario Simétrico/Ejercicio D - Caracter difuso convertido a 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositories\Semestre-EneJun2026\Teoría de la información\AF2\Canal Binario Simétrico\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Repositorios\Semestre-EneJun2026\Teoría de la información\AF2\Canal Binario Simétrico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75CA60AF-A205-48CD-AA87-CDE581970B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6831E8F-9EAF-486F-B963-A9A7FD02CE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D86E2F76-B9DA-43B6-8FD3-A59139A4776F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="20376" windowHeight="12216" xr2:uid="{D86E2F76-B9DA-43B6-8FD3-A59139A4776F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -20,17 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
     </ext>
@@ -39,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Enviar</t>
   </si>
@@ -53,18 +42,6 @@
     <t>Aquí seguimos teniendo un carácter difuso: *</t>
   </si>
   <si>
-    <t>Pero si llega un carácter difuso, en lugar de sólo aceptar que "Bueno no sabemos qué es", lo elegiremos al azar.</t>
-  </si>
-  <si>
-    <t>El receptor lanzará una moneda y según caiga una cara u otra, elegirá si es "0" o "1"</t>
-  </si>
-  <si>
-    <t>Hay que entonces calcular la probabilidad de que salga 1, y 0</t>
-  </si>
-  <si>
-    <t>Ya no puede salir "*" porque lo convertiremos a 1 y 0 usando una mondea justa</t>
-  </si>
-  <si>
     <t>Las probabulidades de que salga 1, son:</t>
   </si>
   <si>
@@ -77,15 +54,6 @@
     <t>Probabilidades de un "*" convertido a 1</t>
   </si>
   <si>
-    <t>Las probabulidades de que salga 0, son:</t>
-  </si>
-  <si>
-    <t>Probabilidad de un 0 legítimo</t>
-  </si>
-  <si>
-    <t>Probabilidades de un "*" convertido a 0</t>
-  </si>
-  <si>
     <t>Enviar 0</t>
   </si>
   <si>
@@ -101,10 +69,31 @@
     <t>Pero expresando esas probabilidades:</t>
   </si>
   <si>
-    <t>p + (r/2)</t>
-  </si>
-  <si>
-    <t>q + (r/2)</t>
+    <t>p</t>
+  </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
+    <t>Ya no puede salir "*" porque lo convertiremos a 1 usando una mondea justa</t>
+  </si>
+  <si>
+    <t>Pero si llega un carácter difuso, en lugar de sólo aceptar que "Bueno no sabemos qué es", lo convertiremos en "1"</t>
+  </si>
+  <si>
+    <t>Entonces descartamos la probabilidad de que salga "0" a partir de un carácter difuso</t>
+  </si>
+  <si>
+    <t>q + r</t>
+  </si>
+  <si>
+    <t>p + r</t>
+  </si>
+  <si>
+    <t>Mientras que las probabilidades de que salga un 0, se reducen solamente a:</t>
+  </si>
+  <si>
+    <t>Probabilidad de entrada de un "0"</t>
   </si>
 </sst>
 </file>
@@ -196,12 +185,6 @@
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="135" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -213,6 +196,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="135" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -555,7 +544,7 @@
   <cols>
     <col min="1" max="1" width="5.33203125" customWidth="1"/>
     <col min="2" max="2" width="3.5546875" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" customWidth="1"/>
+    <col min="3" max="3" width="25.21875" customWidth="1"/>
     <col min="4" max="4" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="33.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.21875" customWidth="1"/>
@@ -570,140 +559,130 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" t="s">
-        <v>14</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="I12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
+      <c r="B13" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="3">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="3">
+        <v>0</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="K16" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="4"/>
-      <c r="B13" s="2" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="4">
+        <v>0</v>
+      </c>
+      <c r="D17" s="4">
         <v>1</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="4"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5">
-        <v>0</v>
-      </c>
-      <c r="D14" s="5">
-        <v>1</v>
-      </c>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" s="5">
-        <v>1</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0</v>
-      </c>
-      <c r="D15" s="6">
-        <v>1</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="5">
-        <v>0</v>
-      </c>
-      <c r="C16" s="6">
-        <v>1</v>
-      </c>
-      <c r="D16" s="6">
-        <v>0</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
-      <c r="B17" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0.5</v>
       </c>
     </row>
   </sheetData>
